--- a/FNDE/Centro Oeste/Entrega/LIMPEZA PREDIAL/fnde_resultado_merge.xlsx
+++ b/FNDE/Centro Oeste/Entrega/LIMPEZA PREDIAL/fnde_resultado_merge.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FNDE_output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3365,56 +3365,58 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>DISPENSADOR PARA PAPEL TOALHA - COMPATÍVEL COM PAPEL INTERFOLHADO.</t>
+          <t>DISPENSADOR PARA PAPEL HIGIÊNICO ROLÃO - COMPATÍVEL COM ROLO DE APROXIMADAMENTE 300 M.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>46306</v>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Calçados para Trabalhar</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>30.420.742/0002-18</t>
+          <t>58.509.800/0001-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>https://www.calcadosparatrabalhar.com.br/dispenser-de-papel-toalha-branco-street-nobre.html</t>
+          <t>https://www.starsprodutosdelimpeza.com.br/dispenser-papel-rolao-300/500m-branco-new-classic-nobre.html</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Papel Toalha Interfolhas Nobre Branco</t>
+          <t>Dispenser Papel Rolão 300/500m Branco New Classic - Nobre</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>46.13</v>
+        <v>29.9</v>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="6" t="n">
-        <v>46.13</v>
+        <v>29.9</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>20.44</v>
+        <v>59.14</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express - Em média 6 dia(s) útil(eis) - R$ 20,44</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 59,14 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P46" s="2" t="n"/>
@@ -3427,12 +3429,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>DISPENSADOR PARA PAPEL TOALHA - COMPATÍVEL COM PAPEL INTERFOLHADO.</t>
+          <t>DISPENSADOR PARA PAPEL HIGIÊNICO ROLÃO - COMPATÍVEL COM ROLO DE APROXIMADAMENTE 300 M.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3440,43 +3442,49 @@
           <t>SP</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>46306</v>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>General Clean</t>
+          <t>VW COMERCIO DE HIDRAULICA E PLASTICOS INDUSTRIAIS LTDA (Plásticos Ipiranga)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>17.587.390/0001-40</t>
+          <t>19.218.815/0001-70</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://www.generalclean.com.br/dispenser-de-papel-toalha</t>
+          <t>https://loja.plasticosipiranga.com.br/dispenser-clean-velox-papel-higienico-rolao-branco</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>DISPENSER DE PAPEL TOALHA INTERFOLHADO</t>
+          <t>Dispenser Clean Velox Papel Higiênico Rolão - Branco</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>62.68</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: compatível com rolo de ~300 m.</t>
+        </is>
+      </c>
       <c r="M47" s="6" t="n">
-        <v>62.68</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>20.53</v>
+        <v>34.77</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .COM R$ 20,53 Previsto para 15/10/2026 até 19/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 34,77 8 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P47" s="2" t="n"/>
@@ -3499,7 +3507,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -3507,38 +3515,38 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>Calçados para Trabalhar</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>30.420.742/0002-18</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/dispenser-papel-toalha/dispenser-para-papel-toalha-fortcom-interfolhado-ou-rolo-dimmt-branco/?PID=71683</t>
+          <t>https://www.calcadosparatrabalhar.com.br/dispenser-de-papel-toalha-branco-street-nobre.html</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Dispenser para Papel Toalha Fortcom Interfolhado ou Rolo DIMMT Branco 1 UN</t>
+          <t>Dispenser Papel Toalha Interfolhas Nobre Branco</t>
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>49.9</v>
+        <v>46.13</v>
       </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="6" t="n">
-        <v>49.9</v>
+        <v>46.13</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>34.65</v>
+        <v>20.44</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Envio: Correios - PAC Valor: R$ 34,65</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express - Em média 6 dia(s) útil(eis) - R$ 20,44</t>
         </is>
       </c>
       <c r="P48" s="2" t="n"/>
@@ -3569,38 +3577,38 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Cauê Distribuidora</t>
+          <t>General Clean</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>34.853.905/0001-26</t>
+          <t>17.587.390/0001-40</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>https://www.distribuidoracaue.com.br/dispenser-para-papel-toalha-interfolhas-2-ou-3-dobras-2-prod.html</t>
+          <t>https://www.generalclean.com.br/dispenser-de-papel-toalha</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Para Papel Toalha Interfolhas 2 Ou 3 Dobras</t>
+          <t>DISPENSER DE PAPEL TOALHA INTERFOLHADO</t>
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>82.17</v>
+        <v>62.68</v>
       </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="6" t="n">
-        <v>82.17</v>
+        <v>62.68</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>21.9</v>
+        <v>20.53</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: PAC - 10 dia(s) útil(eis) R$ 21,90</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .COM R$ 20,53 Previsto para 15/10/2026 até 19/10/2026</t>
         </is>
       </c>
       <c r="P49" s="2" t="n"/>
@@ -3623,46 +3631,46 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Higienize</t>
+          <t>Gimba</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>95.054.177/0001-87</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>https://www.higienize.com/dispensers/dispenser-inox-papel-toalha-interfolhado</t>
+          <t>https://www.gimba.com.br/dispenser-papel-toalha/dispenser-para-papel-toalha-fortcom-interfolhado-ou-rolo-dimmt-branco/?PID=71683</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Inox Papel Toalha Interfolhado</t>
+          <t>Dispenser para Papel Toalha Fortcom Interfolhado ou Rolo DIMMT Branco 1 UN</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>374.29</v>
+        <v>49.9</v>
       </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="6" t="n">
-        <v>374.29</v>
+        <v>49.9</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>37.28</v>
+        <v>34.65</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 37,28 Previsto para 20/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: Envio: Correios - PAC Valor: R$ 34,65</t>
         </is>
       </c>
       <c r="P50" s="2" t="n"/>
@@ -3675,56 +3683,56 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>DISPENSADOR PARA SABONETE LÍQUIDO/ÁLCOOL GEL - DOSADOR PARA SABONETE LÍQUIDO E/OU ÁLCOOL EM GEL.</t>
+          <t>DISPENSADOR PARA PAPEL TOALHA - COMPATÍVEL COM PAPEL INTERFOLHADO.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>Cauê Distribuidora</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>34.853.905/0001-26</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/dispenser-sabonete-alcool-gel-street-c-reservatorio-800ml-xpro</t>
+          <t>https://www.distribuidoracaue.com.br/dispenser-para-papel-toalha-interfolhas-2-ou-3-dobras-2-prod.html</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Sabonete Álcool Gel Street c/ Reservatório 800ml XPRO</t>
+          <t>Dispenser Para Papel Toalha Interfolhas 2 Ou 3 Dobras</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>59.98</v>
+        <v>82.17</v>
       </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="6" t="n">
-        <v>59.98</v>
+        <v>82.17</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>32.18</v>
+        <v>21.9</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 37,54 7 dias úteis Correios PAC R$ 41,14 4 dias úteis Azul Cargo Express - e-commerce</t>
+          <t>Opção mais barata para o CEP 74933-130: PAC - 10 dia(s) útil(eis) R$ 21,90</t>
         </is>
       </c>
       <c r="P51" s="2" t="n"/>
@@ -3737,56 +3745,56 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>DISPENSADOR PARA SABONETE LÍQUIDO/ÁLCOOL GEL - DOSADOR PARA SABONETE LÍQUIDO E/OU ÁLCOOL EM GEL.</t>
+          <t>DISPENSADOR PARA PAPEL TOALHA - COMPATÍVEL COM PAPEL INTERFOLHADO.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Higienize</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>95.054.177/0001-87</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/dispenser-para-sabonete-liquido-espuma-e-alcool-gel/dispenser-para-sabonete-e-alcool-gel-mazzo-com-reservatorio-800ml-1-un/?PID=68121</t>
+          <t>https://www.higienize.com/dispensers/dispenser-inox-papel-toalha-interfolhado</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Dispenser para Sabonete e Álcool Gel Mazzo com Reservatório 800ml 1 UN</t>
+          <t>Dispenser Inox Papel Toalha Interfolhado</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>47.9</v>
+        <v>374.29</v>
       </c>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="6" t="n">
-        <v>47.9</v>
+        <v>374.29</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>32.97</v>
+        <v>37.28</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 32,97 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 37,28 Previsto para 20/10/2026</t>
         </is>
       </c>
       <c r="P52" s="2" t="n"/>
@@ -3809,44 +3817,46 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/casa/dispenser-p-sabonete-liq-alcool-gel-800ml-34031</t>
+          <t>https://www.supriflex.com.br/dispenser-sabonete-alcool-gel-street-c-reservatorio-800ml-xpro</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Dispenser P/ Sabonete Liq Alcool Gel 800ml 34031</t>
+          <t>Dispenser Sabonete Álcool Gel Street c/ Reservatório 800ml XPRO</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>45.9</v>
+        <v>59.98</v>
       </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="6" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="N53" s="2" t="n"/>
+        <v>59.98</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>32.18</v>
+      </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 37,54 7 dias úteis Correios PAC R$ 41,14 4 dias úteis Azul Cargo Express - e-commerce</t>
         </is>
       </c>
       <c r="P53" s="2" t="n"/>
@@ -3869,46 +3879,46 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Higienize</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>95.054.177/0001-87</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>https://www.higienize.com/dispensers/dispenser-inox-sabonete-liquido-500ml</t>
+          <t>https://www.gimba.com.br/dispenser-para-sabonete-liquido-espuma-e-alcool-gel/dispenser-para-sabonete-e-alcool-gel-mazzo-com-reservatorio-800ml-1-un/?PID=68121</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Inox Sabonete Líquido 500ml</t>
+          <t>Dispenser para Sabonete e Álcool Gel Mazzo com Reservatório 800ml 1 UN</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>234.94</v>
+        <v>47.9</v>
       </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="6" t="n">
-        <v>234.94</v>
+        <v>47.9</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>30.18</v>
+        <v>32.97</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 30,18 Previsto para 20/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 32,97 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P54" s="2" t="n"/>
@@ -3921,12 +3931,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>ESCADA ARTICULADA DE ALUMÍNIO – 12 DEGRAUS - USO PROFISSIONAL.</t>
+          <t>DISPENSADOR PARA SABONETE LÍQUIDO/ÁLCOOL GEL - DOSADOR PARA SABONETE LÍQUIDO E/OU ÁLCOOL EM GEL.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3935,35 +3945,35 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Parafusos</t>
+          <t>Fermarcs Ferramentas</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>02.532.281/0001-59</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadosparafusos.com/produto/escada-articulada-12-degraus-3x4-de-aluminio-botafogo-esc0292-102576</t>
+          <t>https://www.fermarcsferramentas.com.br/casa/dispenser-p-sabonete-liq-alcool-gel-800ml-34031</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Escada Articulada 12 Degraus 3x4 de Alumínio - BOTAFOGO-ESC0292</t>
+          <t>Dispenser P/ Sabonete Liq Alcool Gel 800ml 34031</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>919.2</v>
+        <v>45.9</v>
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="6" t="n">
-        <v>919.2</v>
+        <v>45.9</v>
       </c>
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="3" t="inlineStr">
@@ -3981,56 +3991,58 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ESCADA ARTICULADA DE ALUMÍNIO – 12 DEGRAUS - USO PROFISSIONAL.</t>
+          <t>DISPENSADOR PARA SABONETE LÍQUIDO/ÁLCOOL GEL - DOSADOR PARA SABONETE LÍQUIDO E/OU ÁLCOOL EM GEL.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>46307</v>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
+          <t>58.509.800/0001-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>https://www.dutramaquinas.com.br/p/escada-multifuncional-de-aluminio-4-x-3-com-12-degraus-13-em-1-esc0292-esc0292</t>
+          <t>https://www.starsprodutosdelimpeza.com.br/dispenser-plastico-p/sabonete-liquido-/alcool-gel</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Escada multifuncional de alumínio 4 x 3 com 12 degraus 13 em 1 - ESC0292</t>
+          <t>Dispenser P/ Sabonete Liq/Alcool Gel 800ml Ref 9702 - Super Pro Bettanin</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>577.66</v>
+        <v>43.04</v>
       </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="6" t="n">
-        <v>577.66</v>
+        <v>43.04</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>92.08</v>
+        <v>39.26</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 92,08</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 39,26 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P56" s="2" t="n"/>
@@ -4043,12 +4055,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
+          <t>DISPENSADOR PARA SABONETE LÍQUIDO/ÁLCOOL GEL - DOSADOR PARA SABONETE LÍQUIDO E/OU ÁLCOOL EM GEL.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4057,42 +4069,42 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>Higienize</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>95.054.177/0001-87</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/escada-de-aluminio-5-degraus</t>
+          <t>https://www.higienize.com/dispensers/dispenser-inox-sabonete-liquido-500ml</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Escada de Alumínio 5 Degraus</t>
+          <t>Dispenser Inox Sabonete Líquido 500ml</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>198</v>
+        <v>234.94</v>
       </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="6" t="n">
-        <v>198</v>
+        <v>234.94</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>31.54</v>
+        <v>30.18</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 37,87 8 dias úteis Correios - PAC R$ 42,67 6 dias úteis Jadlog - .Com</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 30,18 Previsto para 20/10/2026</t>
         </is>
       </c>
       <c r="P57" s="2" t="n"/>
@@ -4105,12 +4117,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
+          <t>ESCADA ARTICULADA DE ALUMÍNIO – 12 DEGRAUS - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4133,21 +4145,21 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadosparafusos.com/produto/escada-de-fibra-tesoura-pratica-6-degraus-botafogo-efp9901-90140</t>
+          <t>https://www.casadosparafusos.com/produto/escada-articulada-12-degraus-3x4-de-aluminio-botafogo-esc0292-102576</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Escada De Fibra Tesoura Prática 6 Degraus - BOTAFOGO - EFP9901</t>
+          <t>Escada Articulada 12 Degraus 3x4 de Alumínio - BOTAFOGO-ESC0292</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>576.4</v>
+        <v>919.2</v>
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="6" t="n">
-        <v>576.4</v>
+        <v>919.2</v>
       </c>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="3" t="inlineStr">
@@ -4165,12 +4177,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
+          <t>ESCADA ARTICULADA DE ALUMÍNIO – 12 DEGRAUS - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4179,42 +4191,42 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Anhanguera Ferramentas</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>00.565.813/0001-29</t>
+          <t>50.970.342/0001-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>https://www.anhangueraferramentas.com.br/produto/escada-de-aluminio-6-degraus-1-80m-eb-106-alulev-109997</t>
+          <t>https://www.dutramaquinas.com.br/p/escada-multifuncional-de-aluminio-4-x-3-com-12-degraus-13-em-1-esc0292-esc0292</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Escada de Alumínio 6 Degraus 1.80m EB 106 ALULEV</t>
+          <t>Escada multifuncional de alumínio 4 x 3 com 12 degraus 13 em 1 - ESC0292</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>258.73</v>
+        <v>577.66</v>
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="6" t="n">
-        <v>258.73</v>
+        <v>577.66</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>75.03</v>
+        <v>92.08</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Loggi Envio Nacional R$ 75,03 Em até 5 dias úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 92,08</t>
         </is>
       </c>
       <c r="P59" s="2" t="n"/>
@@ -4241,21 +4253,21 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Plast House</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>52.081.713/0001-20</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>https://plasthouse.com.br/produto/comercio/escadas/escada-aluminio-5-degraus-mor/</t>
+          <t>https://www.supriflex.com.br/escada-de-aluminio-5-degraus</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4264,19 +4276,19 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>182.5</v>
+        <v>198</v>
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="6" t="n">
-        <v>182.5</v>
+        <v>198</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>226.43</v>
+        <v>31.54</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Melhor Envio) (7 a 9 dias úteis): R$226,43</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 37,87 8 dias úteis Correios - PAC R$ 42,67 6 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P60" s="2" t="n"/>
@@ -4299,46 +4311,44 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>LF Máquinas e Ferramentas</t>
+          <t>Casa dos Parafusos</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>91.845.735/0004-14</t>
+          <t>02.532.281/0001-59</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>https://www.lfmaquinaseferramentas.com.br/escada-pintor-aluminio-alulev-ap106-profissional-6degraus/p?skuId=16544</t>
+          <t>https://www.casadosparafusos.com/produto/escada-de-fibra-tesoura-pratica-6-degraus-botafogo-efp9901-90140</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Escada Pintor Alumínio Alulev Ap106 Profissional 1,80 Metros 6 Degraus</t>
+          <t>Escada De Fibra Tesoura Prática 6 Degraus - BOTAFOGO - EFP9901</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>926.21</v>
+        <v>576.4</v>
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="6" t="n">
-        <v>926.21</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>103.63</v>
-      </c>
+        <v>576.4</v>
+      </c>
+      <c r="N61" s="2" t="n"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Em até 11 dias úteis R$ 103,63</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P61" s="2" t="n"/>
@@ -4351,17 +4361,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
+          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -4369,38 +4379,38 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>Anhanguera Ferramentas</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>00.565.813/0001-29</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/produto/escova-sanitaria-c-suporte.html</t>
+          <t>https://www.anhangueraferramentas.com.br/produto/escada-de-aluminio-6-degraus-1-80m-eb-106-alulev-109997</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Escova Sanitária c/ Suporte</t>
+          <t>Escada de Alumínio 6 Degraus 1.80m EB 106 ALULEV</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>258.73</v>
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>258.73</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>28.06</v>
+        <v>75.03</v>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 12 dias úteis Correios - Mini Envios R$ 31,54 8 dias úteis Correios PAC R$ 32,18 8 dias úteis Jadlog - .Package</t>
+          <t>Opção mais barata para o CEP 74933-130: Loggi Envio Nacional R$ 75,03 Em até 5 dias úteis</t>
         </is>
       </c>
       <c r="P62" s="2" t="n"/>
@@ -4413,60 +4423,56 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
+          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Plast House</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>52.081.713/0001-20</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/escovas-e-espanadores/escova-para-vaso-sanitario-brubalar-branca-1-un/?PID=78775</t>
+          <t>https://plasthouse.com.br/produto/comercio/escadas/escada-aluminio-5-degraus-mor/</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Escova para Vaso Sanitário Brubalar Branca 1 UN</t>
+          <t>Escada de Alumínio 5 Degraus</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>7.49</v>
+        <v>182.5</v>
       </c>
       <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: com suporte.</t>
-        </is>
-      </c>
+      <c r="L63" s="2" t="n"/>
       <c r="M63" s="6" t="n">
-        <v>7.49</v>
+        <v>182.5</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>30.19</v>
+        <v>226.43</v>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,19 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Melhor Envio) (7 a 9 dias úteis): R$226,43</t>
         </is>
       </c>
       <c r="P63" s="2" t="n"/>
@@ -4479,56 +4485,56 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
+          <t>ESCADA – 5/6 DEGRAUS - USO PROFISSIONAL; DEFINIR MATERIAL E CAPACIDADE DE CARGA ANTES DA PESQUISA.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Cauê Distribuidora</t>
+          <t>LF Máquinas e Ferramentas</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>34.853.905/0001-26</t>
+          <t>91.845.735/0004-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>https://www.distribuidoracaue.com.br/lavatina-com-suporte-escova-sanitaria-prod.html</t>
+          <t>https://www.lfmaquinaseferramentas.com.br/escada-pintor-aluminio-alulev-ap106-profissional-6degraus/p?skuId=16544</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Lavatina Com Suporte / Escova Sanitária</t>
+          <t>Escada Pintor Alumínio Alulev Ap106 Profissional 1,80 Metros 6 Degraus</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>8.99</v>
+        <v>926.21</v>
       </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="6" t="n">
-        <v>8.99</v>
+        <v>926.21</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>18.4</v>
+        <v>103.63</v>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: PAC - 10 dia(s) útil(eis) R$ 18,40</t>
+          <t>Opção mais barata para o CEP 74933-130: Em até 11 dias úteis R$ 103,63</t>
         </is>
       </c>
       <c r="P64" s="2" t="n"/>
@@ -4551,7 +4557,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -4559,38 +4565,38 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Casa do Saco de Lixo</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>02.236.630/0001-95</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>https://loja.casadosacodelixo.com.br/escova-sanitaria-com-suporte-2024-05-14-16-11-31</t>
+          <t>https://www.supriflex.com.br/produto/escova-sanitaria-c-suporte.html</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Escova sanitária com suporte (Modelo: Betthavale)</t>
+          <t>Escova Sanitária c/ Suporte</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>11.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="6" t="n">
-        <v>11.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>27.42</v>
+        <v>28.06</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 12 dias úteis Correios - Mini Envios R$ 31,54 8 dias úteis Correios PAC R$ 32,18 8 dias úteis Jadlog - .Package</t>
         </is>
       </c>
       <c r="P65" s="2" t="n"/>
@@ -4621,35 +4627,45 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="n"/>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/escovas-e-espanadores/escova-para-vaso-sanitario-brubalar-branca-1-un/?PID=78775</t>
+        </is>
+      </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Escova Sanitária Com Suporte Condor</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n"/>
+          <t>Escova para Vaso Sanitário Brubalar Branca 1 UN</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>7.49</v>
+      </c>
       <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: com suporte.</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>30.19</v>
+      </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ncbelladistribuidora.com.br/escova-sanitaria-com-suporte-condor</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,19 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4659,12 +4675,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
+          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4673,46 +4689,42 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Cauê Distribuidora</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>34.853.905/0001-26</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/escovas-e-espanadores/espanador-perfect-pro-eletrostatico-com-cabo-1-un/?PID=203679</t>
+          <t>https://www.distribuidoracaue.com.br/lavatina-com-suporte-escova-sanitaria-prod.html</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Espanador Perfect Pro Eletrostático com Cabo 1 UN</t>
+          <t>Lavatina Com Suporte / Escova Sanitária</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>46.19</v>
+        <v>8.99</v>
       </c>
       <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo mínimo 50 cm.</t>
-        </is>
-      </c>
+      <c r="L67" s="2" t="n"/>
       <c r="M67" s="6" t="n">
-        <v>46.19</v>
+        <v>8.99</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>77.55</v>
+        <v>18.4</v>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,55 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: PAC - 10 dia(s) útil(eis) R$ 18,40</t>
         </is>
       </c>
       <c r="P67" s="2" t="n"/>
@@ -4725,17 +4737,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
+          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -4743,42 +4755,38 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>Casa do Saco de Lixo</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
+          <t>02.236.630/0001-95</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncbelladistribuidora.com.br/espanador-eletrostatico-azul-certec</t>
+          <t>https://loja.casadosacodelixo.com.br/escova-sanitaria-com-suporte-2024-05-14-16-11-31</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Espanador Eletrostático Azul - Certec</t>
+          <t>Escova sanitária com suporte (Modelo: Betthavale)</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>44</v>
+        <v>11.25</v>
       </c>
       <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo mínimo 50 cm.</t>
-        </is>
-      </c>
+      <c r="L68" s="2" t="n"/>
       <c r="M68" s="6" t="n">
-        <v>44</v>
+        <v>11.25</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>16.97</v>
+        <v>27.42</v>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 16,97 8 dias úteis Loggi - Express</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P68" s="2" t="n"/>
@@ -4791,53 +4799,61 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
+          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>46308</v>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="n"/>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/escova-sanitaria-com-pote</t>
+        </is>
+      </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Espanador de Penas Nº35 50cm</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="n"/>
+          <t>Escova Sanitária Com Suporte - Rodo 2000</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>10.9</v>
+      </c>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="2" t="n"/>
+      <c r="M69" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>36.64</v>
+      </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/produto/espanador-de-penas-no35.html</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4847,12 +4863,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>EXTENSÃO ELÉTRICA – 30 M - USO COMPATÍVEL COM EQUIPAMENTOS DE LIMPEZA.</t>
+          <t>ESCOVA PARA VASO SANITÁRIO - COM SUPORTE.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4861,45 +4877,39 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>https://www.dutramaquinas.com.br/p/extensao-eletrica-30-metros-3-x-2-50-mm-2pt-20a-com-carretel-0181200014</t>
-        </is>
-      </c>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Extensão elétrica 30 metros 3 x 2,50 mm 2P+T 20A com carretel</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="n">
-        <v>640.9</v>
-      </c>
+          <t>Escova Sanitária Com Suporte Condor</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
-      <c r="M70" s="6" t="n">
-        <v>640.9</v>
-      </c>
-      <c r="N70" s="6" t="n">
-        <v>46.24</v>
-      </c>
+      <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 10 a 12 dias úteis R$ 46,24</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/escova-sanitaria-com-suporte-condor</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4909,12 +4919,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>EXTENSÃO ELÉTRICA – 30 M - USO COMPATÍVEL COM EQUIPAMENTOS DE LIMPEZA.</t>
+          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4927,38 +4937,42 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Anhanguera Ferramentas</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>00.565.813/0001-29</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>https://www.anhangueraferramentas.com.br/produto/extensao-eletrica-carretel-pp-3x2-5mm-30m-20a-1547-maxi-pro-daneva-106726</t>
+          <t>https://www.gimba.com.br/escovas-e-espanadores/espanador-perfect-pro-eletrostatico-com-cabo-1-un/?PID=203679</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Extensão Elétrica Carretel PP 3x2.5mm² 30m 20A 1547 MAXI PRO DANEVA</t>
+          <t>Espanador Perfect Pro Eletrostático com Cabo 1 UN</t>
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>723.41</v>
+        <v>46.19</v>
       </c>
       <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo mínimo 50 cm.</t>
+        </is>
+      </c>
       <c r="M71" s="6" t="n">
-        <v>723.41</v>
+        <v>46.19</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>41.44</v>
+        <v>77.55</v>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Loggi Envio Nacional R$ 41,44 Em até 5 dias úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,55 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P71" s="2" t="n"/>
@@ -4971,12 +4985,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
+          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4989,38 +5003,42 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>57.935.095/0001-52</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-mondial-aqua-power-i-1400w-220v-lap01gy-cinza-com-amarelo-1-un/?PID=204324</t>
+          <t>https://www.ncbelladistribuidora.com.br/espanador-eletrostatico-azul-certec</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Lavadora de Alta Pressão Mondial Aqua Power I 1400W 220V LAP-01-GY Cinza com Amarelo 1 UN</t>
+          <t>Espanador Eletrostático Azul - Certec</t>
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>577.05</v>
+        <v>44</v>
       </c>
       <c r="K72" s="2" t="n"/>
-      <c r="L72" s="2" t="n"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo mínimo 50 cm.</t>
+        </is>
+      </c>
       <c r="M72" s="6" t="n">
-        <v>577.05</v>
+        <v>44</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>80.98</v>
+        <v>16.97</v>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 80,98 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 16,97 8 dias úteis Loggi - Express</t>
         </is>
       </c>
       <c r="P72" s="2" t="n"/>
@@ -5033,54 +5051,62 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
+          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>46308</v>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>58.509.800/0001-12</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/lavadora-de-alta-pressao-karcher-profissional-hd-585-profi/p</t>
+          <t>https://www.starsprodutosdelimpeza.com.br/espanador-soft-de-microfibra-kd-d11-nobre</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Lavadora de Alta Pressão Kärcher HD 585 Profi 2176 PSI 2200W Profissional | 220V</t>
+          <t>Espanador soft de microfibra (KD-D11) - Nobre</t>
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>2659.9</v>
+        <v>17.57</v>
       </c>
       <c r="K73" s="2" t="n"/>
-      <c r="L73" s="2" t="n"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo mínimo de 50 cm.</t>
+        </is>
+      </c>
       <c r="M73" s="6" t="n">
-        <v>2659.9</v>
-      </c>
-      <c r="N73" s="2" t="n"/>
+        <v>17.57</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>36.64</v>
+      </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P73" s="2" t="n"/>
@@ -5093,17 +5119,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
+          <t>ESPANADOR - CABO MÍNIMO DE 50 CM.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -5111,39 +5137,35 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>https://www.fermarcsferramentas.com.br/ferramentas-e-maquinas/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-k3-acqua-jet-220v-000000000019943260</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Lavadora De Alta Pressao K3 Acqua Jet 220v 000000000019943260</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>1089.9</v>
-      </c>
+          <t>Espanador de Penas Nº35 50cm</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
-      <c r="M74" s="6" t="n">
-        <v>1089.9</v>
-      </c>
+      <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="n"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/espanador-de-penas-no35.html</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5153,54 +5175,56 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
+          <t>EXTENSÃO ELÉTRICA – 30 M - USO COMPATÍVEL COM EQUIPAMENTOS DE LIMPEZA.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>50.970.342/0001-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/27281-lavadora-de-alta-pressao-profissional-jacto-j7300-2700-psi-cor-laranja-220v-jacto</t>
+          <t>https://www.dutramaquinas.com.br/p/extensao-eletrica-30-metros-3-x-2-50-mm-2pt-20a-com-carretel-0181200014</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Lavadora De Alta Pressão Profissional Jacto J7300 2700 Psi Cor Laranja 220v - JACTO</t>
+          <t>Extensão elétrica 30 metros 3 x 2,50 mm 2P+T 20A com carretel</t>
         </is>
       </c>
       <c r="J75" s="6" t="n">
-        <v>2989</v>
+        <v>640.9</v>
       </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="6" t="n">
-        <v>2989</v>
-      </c>
-      <c r="N75" s="2" t="n"/>
+        <v>640.9</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>46.24</v>
+      </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: 10 a 12 dias úteis R$ 46,24</t>
         </is>
       </c>
       <c r="P75" s="2" t="n"/>
@@ -5213,54 +5237,56 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
+          <t>EXTENSÃO ELÉTRICA – 30 M - USO COMPATÍVEL COM EQUIPAMENTOS DE LIMPEZA.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Parafusos</t>
+          <t>Anhanguera Ferramentas</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>02.532.281/0001-59</t>
+          <t>00.565.813/0001-29</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadosparafusos.com/produto/lavadora-de-alta-pressao-hd-585-profissional-2176psi-2200w-220v-karcher-19741850-89483</t>
+          <t>https://www.anhangueraferramentas.com.br/produto/extensao-eletrica-carretel-pp-3x2-5mm-30m-20a-1547-maxi-pro-daneva-106726</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Lavadora de Alta Pressão HD 585 Profissional 2176PSI 2200W 220V KARCHER-19741850</t>
+          <t>Extensão Elétrica Carretel PP 3x2.5mm² 30m 20A 1547 MAXI PRO DANEVA</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>3693.12</v>
+        <v>723.41</v>
       </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="6" t="n">
-        <v>3693.12</v>
-      </c>
-      <c r="N76" s="2" t="n"/>
+        <v>723.41</v>
+      </c>
+      <c r="N76" s="6" t="n">
+        <v>41.44</v>
+      </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: Loggi Envio Nacional R$ 41,44 Em até 5 dias úteis</t>
         </is>
       </c>
       <c r="P76" s="2" t="n"/>
@@ -5283,7 +5309,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5291,35 +5317,41 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>09.636.445/0001-37</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n"/>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-mondial-aqua-power-i-1400w-220v-lap01gy-cinza-com-amarelo-1-un/?PID=204324</t>
+        </is>
+      </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Lavadora De Alta Pressão Karcher Profissional Hd 4/10 X Clas Cinza 60 Hz</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n"/>
+          <t>Lavadora de Alta Pressão Mondial Aqua Power I 1400W 220V LAP-01-GY Cinza com Amarelo 1 UN</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>577.05</v>
+      </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
+      <c r="M77" s="6" t="n">
+        <v>577.05</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>80.98</v>
+      </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 2671,63)</t>
-        </is>
-      </c>
-      <c r="P77" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hpmaquinas.com.br/marcas/karcher/lavadoras-de-alta-pressao-profissionais/lavadora-de-alta-pressao-karcher-profissional-hd-4-10-x-clas-cinza-60-hz</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 80,98 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5339,7 +5371,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -5347,35 +5379,39 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="n"/>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/lavadora-de-alta-pressao-karcher-profissional-hd-585-profi/p</t>
+        </is>
+      </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Lavadora de Alta Pressão Jacto J6000 220V</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="n"/>
+          <t>Lavadora de Alta Pressão Kärcher HD 585 Profi 2176 PSI 2200W Profissional | 220V</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>2659.9</v>
+      </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="6" t="n">
+        <v>2659.9</v>
+      </c>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P78" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ncbelladistribuidora.com.br/lavadora-de-alta-pressao-jacto-j6000-220v</t>
-        </is>
-      </c>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5385,12 +5421,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
+          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5403,31 +5439,31 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/aspirador-po-agua-jacto-aj22-22l-1200w-inox/p</t>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-e-maquinas/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-k3-acqua-jet-220v-000000000019943260</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Aspirador de Pó e Água Jacto AJ22 22L 1200W Inox Profissional | 220V</t>
+          <t>Lavadora De Alta Pressao K3 Acqua Jet 220v 000000000019943260</t>
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>569.05</v>
+        <v>1089.9</v>
       </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="6" t="n">
-        <v>569.05</v>
+        <v>1089.9</v>
       </c>
       <c r="N79" s="2" t="n"/>
       <c r="O79" s="3" t="inlineStr">
@@ -5445,12 +5481,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
+          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5459,40 +5495,40 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/aspirador-de-poagua-ecoclean-220v</t>
+          <t>https://www.goiasferramentas.com.br/produto/27281-lavadora-de-alta-pressao-profissional-jacto-j7300-2700-psi-cor-laranja-220v-jacto</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Aspirador De Po/Agua Ecoclean 220v Ap120-220</t>
+          <t>Lavadora De Alta Pressão Profissional Jacto J7300 2700 Psi Cor Laranja 220v - JACTO</t>
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>799.9</v>
+        <v>2989</v>
       </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="6" t="n">
-        <v>799.9</v>
+        <v>2989</v>
       </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P80" s="2" t="n"/>
@@ -5505,56 +5541,54 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
+          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>LF Máquinas e Ferramentas</t>
+          <t>Casa dos Parafusos</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>91.845.735/0004-14</t>
+          <t>02.532.281/0001-59</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>https://www.lfmaquinaseferramentas.com.br/aspirador-de-po-e-liquido-industrial-dewalt-30l-1500w/p?skuId=127326</t>
+          <t>https://www.casadosparafusos.com/produto/lavadora-de-alta-pressao-hd-585-profissional-2176psi-2200w-220v-karcher-19741850-89483</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Aspirador de Pó e Líquido Industrial Dewalt 30L 1500W</t>
+          <t>Lavadora de Alta Pressão HD 585 Profissional 2176PSI 2200W 220V KARCHER-19741850</t>
         </is>
       </c>
       <c r="J81" s="6" t="n">
-        <v>2849</v>
+        <v>3693.12</v>
       </c>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="6" t="n">
-        <v>2849</v>
-      </c>
-      <c r="N81" s="6" t="n">
-        <v>61.7</v>
-      </c>
+        <v>3693.12</v>
+      </c>
+      <c r="N81" s="2" t="n"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Em até 9 dias úteis R$ 61,70</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P81" s="2" t="n"/>
@@ -5567,17 +5601,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
+          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -5585,39 +5619,35 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>https://www.casadopicapau.com.br/aspirador-de-po-e-agua-inox-12l-1700w-karcher-wdl-1s/p</t>
-        </is>
-      </c>
+          <t>09.636.445/0001-37</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Aspirador de Pó e Água Inox 12L 1700W Kärcher WDL 1s | 220V</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="n">
-        <v>446.4</v>
-      </c>
+          <t>Lavadora De Alta Pressão Karcher Profissional Hd 4/10 X Clas Cinza 60 Hz</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n"/>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
-      <c r="M82" s="6" t="n">
-        <v>446.4</v>
-      </c>
+      <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="n"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="n"/>
+          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 2671,63)</t>
+        </is>
+      </c>
+      <c r="P82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hpmaquinas.com.br/marcas/karcher/lavadoras-de-alta-pressao-profissionais/lavadora-de-alta-pressao-karcher-profissional-hd-4-10-x-clas-cinza-60-hz</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5627,17 +5657,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
+          <t>LAVADORA DE ALTA PRESSÃO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -5645,39 +5675,35 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>https://www.fermarcsferramentas.com.br/ferramentas-manuais/aspiradores-de-po/aspirador-de-poagua-3100-mono-1600w-30l-14287210</t>
-        </is>
-      </c>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Aspirador De Po/Agua 3100 Mono 1600w 30l 14287210</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>988</v>
-      </c>
+          <t>Lavadora de Alta Pressão Jacto J6000 220V</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="n"/>
-      <c r="M83" s="6" t="n">
-        <v>988</v>
-      </c>
+      <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/lavadora-de-alta-pressao-jacto-j6000-220v</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5687,56 +5713,54 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>https://www.dutramaquinas.com.br/p/aspirador-de-po-e-liquido-30-litros-1-600-watts-nt3000-14287150</t>
+          <t>https://www.casadopicapau.com.br/aspirador-po-agua-jacto-aj22-22l-1200w-inox/p</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Aspirador de pó e líquido 30 litros 1.600 watts - NT3000 110V</t>
+          <t>Aspirador de Pó e Água Jacto AJ22 22L 1200W Inox Profissional | 220V</t>
         </is>
       </c>
       <c r="J84" s="6" t="n">
-        <v>711</v>
+        <v>569.05</v>
       </c>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="6" t="n">
-        <v>711</v>
-      </c>
-      <c r="N84" s="6" t="n">
-        <v>94.66</v>
-      </c>
+        <v>569.05</v>
+      </c>
+      <c r="N84" s="2" t="n"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 94,66</t>
+          <t>Frete grátis para o CEP 74933-130</t>
         </is>
       </c>
       <c r="P84" s="2" t="n"/>
@@ -5749,12 +5773,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5767,31 +5791,31 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
+          <t>https://www.fermarcsferramentas.com.br/aspirador-de-poagua-ecoclean-220v</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
+          <t>Aspirador De Po/Agua Ecoclean 220v Ap120-220</t>
         </is>
       </c>
       <c r="J85" s="6" t="n">
-        <v>3419.9</v>
+        <v>799.9</v>
       </c>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="6" t="n">
-        <v>3419.9</v>
+        <v>799.9</v>
       </c>
       <c r="N85" s="2" t="n"/>
       <c r="O85" s="3" t="inlineStr">
@@ -5809,17 +5833,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ INDUSTRIAL - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -5827,35 +5851,41 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
+          <t>LF Máquinas e Ferramentas</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>09.636.445/0001-37</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="n"/>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/aspirador-de-po-e-liquido-industrial-dewalt-30l-1500w/p?skuId=127326</t>
+        </is>
+      </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n"/>
+          <t>Aspirador de Pó e Líquido Industrial Dewalt 30L 1500W</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>2849</v>
+      </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="2" t="n"/>
+      <c r="M86" s="6" t="n">
+        <v>2849</v>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>61.7</v>
+      </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
-        </is>
-      </c>
-      <c r="P86" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Em até 9 dias úteis R$ 61,70</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5865,17 +5895,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -5883,35 +5913,39 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="n"/>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/aspirador-de-po-e-agua-inox-12l-1700w-karcher-wdl-1s/p</t>
+        </is>
+      </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n"/>
+          <t>Aspirador de Pó e Água Inox 12L 1700W Kärcher WDL 1s | 220V</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>446.4</v>
+      </c>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="n"/>
-      <c r="M87" s="2" t="n"/>
+      <c r="M87" s="6" t="n">
+        <v>446.4</v>
+      </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P87" s="5" t="inlineStr">
-        <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
-        </is>
-      </c>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5921,17 +5955,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -5939,31 +5973,31 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncbelladistribuidora.com.br/enceradeira-piso-270-c1-escada-bivolt-certec</t>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-manuais/aspiradores-de-po/aspirador-de-poagua-3100-mono-1600w-30l-14287210</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Piso 270 C1 Escada Bivolt – CERTEC</t>
+          <t>Aspirador De Po/Agua 3100 Mono 1600w 30l 14287210</t>
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>3473</v>
+        <v>988</v>
       </c>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="6" t="n">
-        <v>3473</v>
+        <v>988</v>
       </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="3" t="inlineStr">
@@ -5981,54 +6015,56 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
+          <t>ASPIRADOR DE PÓ – MÍNIMO 1.600 W - USO GERAL/PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>50.970.342/0001-02</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
+          <t>https://www.dutramaquinas.com.br/p/aspirador-de-po-e-liquido-30-litros-1-600-watts-nt3000-14287150</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
+          <t>Aspirador de pó e líquido 30 litros 1.600 watts - NT3000 110V</t>
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>3419.9</v>
+        <v>711</v>
       </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="6" t="n">
-        <v>3419.9</v>
-      </c>
-      <c r="N89" s="2" t="n"/>
+        <v>711</v>
+      </c>
+      <c r="N89" s="6" t="n">
+        <v>94.66</v>
+      </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
+          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 94,66</t>
         </is>
       </c>
       <c r="P89" s="2" t="n"/>
@@ -6041,56 +6077,54 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>https://www.dutramaquinas.com.br/p/lavadora-secadora-de-piso-eletrica-1100w-510-mm-50l-bd-50-50-c-classic-19943610</t>
+          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>Lavadora Secadora de Piso Elétrica 1100W 510 mm 50L - BD 50/50 C Classic 220V</t>
+          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>17198.88</v>
+        <v>3419.9</v>
       </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="6" t="n">
-        <v>17198.88</v>
-      </c>
-      <c r="N90" s="6" t="n">
-        <v>605.5700000000001</v>
-      </c>
+        <v>3419.9</v>
+      </c>
+      <c r="N90" s="2" t="n"/>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 5 a 8 dias úteis R$ 605,57</t>
+          <t>Frete grátis para o CEP 74933-130</t>
         </is>
       </c>
       <c r="P90" s="2" t="n"/>
@@ -6103,53 +6137,63 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>46308</v>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>09.636.445/0001-37</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="n"/>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/enceradeira-linha-c-200-rpm-410mm-bivolt-certec</t>
+        </is>
+      </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="n"/>
+          <t>Enceradeira Linha C 200 Rpm 410mm Bivolt Certec</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>4641</v>
+      </c>
       <c r="K91" s="2" t="n"/>
-      <c r="L91" s="2" t="n"/>
-      <c r="M91" s="2" t="n"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: porte grande.</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>4641</v>
+      </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
-        </is>
-      </c>
-      <c r="P91" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6159,17 +6203,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -6177,18 +6221,18 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>09.636.445/0001-37</t>
         </is>
       </c>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
+          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
         </is>
       </c>
       <c r="J92" s="2" t="n"/>
@@ -6198,12 +6242,12 @@
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
+          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
         </is>
       </c>
       <c r="P92" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
+          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
         </is>
       </c>
     </row>
@@ -6215,17 +6259,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – GRANDE - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
@@ -6233,39 +6277,35 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ncbelladistribuidora.com.br/enceradeira-piso-270-c1-escada-bivolt-certec</t>
-        </is>
-      </c>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n"/>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Piso 270 C1 Escada Bivolt – CERTEC</t>
-        </is>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>3473</v>
-      </c>
+          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n"/>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="n"/>
-      <c r="M93" s="6" t="n">
-        <v>3473</v>
-      </c>
+      <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6275,17 +6315,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -6293,31 +6333,31 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>57.935.095/0001-52</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
+          <t>https://www.ncbelladistribuidora.com.br/enceradeira-piso-270-c1-escada-bivolt-certec</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
+          <t>Enceradeira Piso 270 C1 Escada Bivolt – CERTEC</t>
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>3419.9</v>
+        <v>3473</v>
       </c>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="6" t="n">
-        <v>3419.9</v>
+        <v>3473</v>
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="3" t="inlineStr">
@@ -6335,17 +6375,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -6353,35 +6393,39 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>09.636.445/0001-37</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="n"/>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
+        </is>
+      </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="n"/>
+          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>3419.9</v>
+      </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
-      <c r="M95" s="2" t="n"/>
+      <c r="M95" s="6" t="n">
+        <v>3419.9</v>
+      </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
-        </is>
-      </c>
-      <c r="P95" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
-        </is>
-      </c>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6391,53 +6435,59 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="n"/>
+          <t>50.970.342/0001-02</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dutramaquinas.com.br/p/lavadora-secadora-de-piso-eletrica-1100w-510-mm-50l-bd-50-50-c-classic-19943610</t>
+        </is>
+      </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n"/>
+          <t>Lavadora Secadora de Piso Elétrica 1100W 510 mm 50L - BD 50/50 C Classic 220V</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>17198.88</v>
+      </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="n"/>
-      <c r="M96" s="2" t="n"/>
-      <c r="N96" s="2" t="n"/>
+      <c r="M96" s="6" t="n">
+        <v>17198.88</v>
+      </c>
+      <c r="N96" s="6" t="n">
+        <v>605.5700000000001</v>
+      </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P96" s="5" t="inlineStr">
-        <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: 5 a 8 dias úteis R$ 605,57</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6447,17 +6497,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO CURTO - PLÁSTICA OU METÁLICA.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -6465,45 +6515,35 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gimba.com.br/pas-de-lixo/pa-coletora-de-lixo-perfect-pro-com-alca-1-un/?PID=203675</t>
-        </is>
-      </c>
+          <t>09.636.445/0001-37</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n"/>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Pa Coletora de Lixo Perfect Pro com Alça 1 UN</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>26.99</v>
-      </c>
+          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="n"/>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: plástica ou metálica, cabo curto.</t>
-        </is>
-      </c>
-      <c r="M97" s="6" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="N97" s="6" t="n">
-        <v>77.42</v>
-      </c>
+      <c r="L97" s="2" t="n"/>
+      <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,42 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="n"/>
+          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
+        </is>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6513,17 +6553,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO CURTO - PLÁSTICA OU METÁLICA.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – MÉDIA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -6531,45 +6571,35 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/produto/pa-de-lixo-c-cabo-grande.html</t>
-        </is>
-      </c>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n"/>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>Pá de Lixo Grande c/ Cabo Ref.: D057</t>
-        </is>
-      </c>
-      <c r="J98" s="6" t="n">
-        <v>8.98</v>
-      </c>
+          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n"/>
       <c r="K98" s="2" t="n"/>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: plástica ou metálica, cabo curto.</t>
-        </is>
-      </c>
-      <c r="M98" s="6" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="N98" s="6" t="n">
-        <v>89.84999999999999</v>
-      </c>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 89,85 7 dias úteis Correios PAC</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6579,17 +6609,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -6597,38 +6627,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>57.935.095/0001-52</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/pa-de-lixo-jeitosa-superpro-articulada-com-cabo</t>
+          <t>https://www.ncbelladistribuidora.com.br/enceradeira-piso-270-c1-escada-bivolt-certec</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>Pá de Lixo Jeitosa Articulada c/ Cabo</t>
+          <t>Enceradeira Piso 270 C1 Escada Bivolt – CERTEC</t>
         </is>
       </c>
       <c r="J99" s="6" t="n">
-        <v>25.63</v>
+        <v>3473</v>
       </c>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="6" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="N99" s="6" t="n">
-        <v>103.38</v>
-      </c>
+        <v>3473</v>
+      </c>
+      <c r="N99" s="2" t="n"/>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 103,38 7 dias úteis Correios PAC R$ 115,69 8 dias úteis Correios - PAC R$ 121,19 4 dias úteis Azul Cargo Express - e-commerce</t>
+          <t>Frete grátis para o CEP 74933-130</t>
         </is>
       </c>
       <c r="P99" s="2" t="n"/>
@@ -6641,17 +6669,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -6659,42 +6687,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncbelladistribuidora.com.br/pa-coletora-preto-certec</t>
+          <t>https://www.casadopicapau.com.br/enceradeira-industrial-cl-400-plus-cleaner/p</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>Pá Coletora Preto Certec</t>
+          <t>Enceradeira Industrial CL-400 Plus Sales Cleaner | 220V</t>
         </is>
       </c>
       <c r="J100" s="6" t="n">
-        <v>44</v>
+        <v>3419.9</v>
       </c>
       <c r="K100" s="2" t="n"/>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo longo.</t>
-        </is>
-      </c>
+      <c r="L100" s="2" t="n"/>
       <c r="M100" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="N100" s="6" t="n">
-        <v>18.45</v>
-      </c>
+        <v>3419.9</v>
+      </c>
+      <c r="N100" s="2" t="n"/>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,45 8 dias úteis Loggi - Express</t>
+          <t>Frete grátis para o CEP 74933-130</t>
         </is>
       </c>
       <c r="P100" s="2" t="n"/>
@@ -6707,17 +6729,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -6725,39 +6747,35 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>https://www.fermarcsferramentas.com.br/ferramentas-manuais/ferramentas-manuais/pa-para-lixo-c-cabo-100388</t>
-        </is>
-      </c>
+          <t>09.636.445/0001-37</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n"/>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Pa Para Lixo C/ Cabo 100388</t>
-        </is>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>20.9</v>
-      </c>
+          <t>Lavadora e Secadora de Piso Karcher BD 50/50 C Classic - 220V</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n"/>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
-      <c r="M101" s="6" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
-        </is>
-      </c>
-      <c r="P101" s="2" t="n"/>
+          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 19180,03)</t>
+        </is>
+      </c>
+      <c r="P101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hpmaquinas.com.br/segmentos/limpeza/lavadora-e-secadora-de-piso-bd-5050-c-classic-eletrica-kaercher-220v</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6767,59 +6785,53 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
+          <t>ENCERADEIRA/LAVADORA DE PISO – PEQUENA - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>General Clean</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>17.587.390/0001-40</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>https://www.generalclean.com.br/pa-de-lixo-plastica-cabo-longo</t>
-        </is>
-      </c>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n"/>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>PA DE LIXO PLASTICA CABO LONGO 40CM</t>
-        </is>
-      </c>
-      <c r="J102" s="6" t="n">
-        <v>6.98</v>
-      </c>
+          <t>Enceradeira Ind. Plus CL400 110v ou 220v - Cleaner</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n"/>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
-      <c r="M102" s="6" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="N102" s="6" t="n">
-        <v>46.6</v>
-      </c>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: CORREIOS PAC R$ 46,60 Previsto para 20/10/2026 até 22/10/2026</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/enceradeira-ind.-plus-cl400-110v-ou-220v-cleaner</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6829,56 +6841,60 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
+          <t>MANGUEIRA – 50 M - COM BICO/ESGUICHO COMPATÍVEL.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="n">
-        <v>46307</v>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>https://www.dutramaquinas.com.br/p/pa-coletora-de-lixo-cabo-de-madeira-revestido-com-plastico-pop-pp555</t>
+          <t>https://www.casadopicapau.com.br/mangueira-polietileno-25mm-3mm-rolo-50m-tramontina/p</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>Pá coletora de lixo cabo de madeira POP - PP555</t>
+          <t>Mangueira Polietileno 25mm x 3mm Rolo de 50m - Tramontina</t>
         </is>
       </c>
       <c r="J103" s="6" t="n">
-        <v>79.90000000000001</v>
+        <v>557.33</v>
       </c>
       <c r="K103" s="2" t="n"/>
-      <c r="L103" s="2" t="n"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Tubo de polietileno 25 mm aceito como mangueira (decisão de 14/10/2026); bico/esguicho não confirmado na página.</t>
+        </is>
+      </c>
       <c r="M103" s="6" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="N103" s="6" t="n">
-        <v>25.21</v>
-      </c>
+        <v>557.33</v>
+      </c>
+      <c r="N103" s="2" t="n"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 8 a 10 dias úteis R$ 25,21</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P103" s="2" t="n"/>
@@ -6891,60 +6907,60 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
+          <t>MANGUEIRA – 100 M - COM BICO/ESGUICHO COMPATÍVEL.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>46308</v>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/pas-de-lixo/pa-coletora-com-cabo-bralimpia-pop-plastica-azul-pp555-1-un/?PID=25627</t>
+          <t>https://www.casadopicapau.com.br/mangueira-polietileno-25mm-3mm-rolo-100m-tramontina/p</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>Pá Coletora com Cabo Bralimpia Pop Plástica Azul PP555 1 UN</t>
+          <t>Mangueira Polietileno 25mm x 3mm Rolo de 100m - Tramontina</t>
         </is>
       </c>
       <c r="J104" s="6" t="n">
-        <v>69.98999999999999</v>
+        <v>1114.66</v>
       </c>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: tampa basculante, cabo longo.</t>
+          <t>Tubo de polietileno 25 mm aceito como mangueira (decisão de 14/10/2026); bico/esguicho não confirmado na página.</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="N104" s="6" t="n">
-        <v>77.69</v>
-      </c>
+        <v>1114.66</v>
+      </c>
+      <c r="N104" s="2" t="n"/>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,69 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P104" s="2" t="n"/>
@@ -6957,60 +6973,60 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
+          <t>PÁ COLETORA DE LIXO – CABO CURTO - PLÁSTICA OU METÁLICA.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Casa do Saco de Lixo</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>02.236.630/0001-95</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>https://loja.casadosacodelixo.com.br/pa-coletora-novica</t>
+          <t>https://www.gimba.com.br/pas-de-lixo/pa-coletora-de-lixo-perfect-pro-com-alca-1-un/?PID=203675</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Pá Coletora Noviça</t>
+          <t>Pa Coletora de Lixo Perfect Pro com Alça 1 UN</t>
         </is>
       </c>
       <c r="J105" s="6" t="n">
-        <v>39.8</v>
+        <v>26.99</v>
       </c>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: tampa basculante.</t>
+          <t>Característica não confirmada na página do produto: plástica ou metálica, cabo curto.</t>
         </is>
       </c>
       <c r="M105" s="6" t="n">
-        <v>39.8</v>
+        <v>26.99</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>27.42</v>
+        <v>77.42</v>
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,42 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P105" s="2" t="n"/>
@@ -7023,12 +7039,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
+          <t>PÁ COLETORA DE LIXO – CABO CURTO - PLÁSTICA OU METÁLICA.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -7037,46 +7053,46 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Higienize</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>95.054.177/0001-87</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>https://www.higienize.com/equipamentos/pa-coletora-com-tampa-bettanin</t>
+          <t>https://www.supriflex.com.br/produto/pa-de-lixo-c-cabo-grande.html</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>Pá Coletora com Tampa Bettanin</t>
+          <t>Pá de Lixo Grande c/ Cabo Ref.: D057</t>
         </is>
       </c>
       <c r="J106" s="6" t="n">
-        <v>58.49</v>
+        <v>8.98</v>
       </c>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: cabo longo.</t>
+          <t>Característica não confirmada na página do produto: plástica ou metálica, cabo curto.</t>
         </is>
       </c>
       <c r="M106" s="6" t="n">
-        <v>58.49</v>
+        <v>8.98</v>
       </c>
       <c r="N106" s="6" t="n">
-        <v>30.14</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 30,14 Previsto para 20/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 89,85 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P106" s="2" t="n"/>
@@ -7089,56 +7105,56 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – BANHEIRO INTERDITADO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Profissional da Limpeza</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>45.343.703/0001-50</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>https://profissionaldalimpeza.commercesuite.com.br/equipamentos/placa-de-sinalizacao/placa-de-sinalizacao-banheiro-fora-de-uso</t>
+          <t>https://www.supriflex.com.br/pa-de-lixo-jeitosa-superpro-articulada-com-cabo</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Placa de Sinalização Banheiro Fora de Uso</t>
+          <t>Pá de Lixo Jeitosa Articulada c/ Cabo</t>
         </is>
       </c>
       <c r="J107" s="6" t="n">
-        <v>24.9</v>
+        <v>25.63</v>
       </c>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="6" t="n">
-        <v>24.9</v>
+        <v>25.63</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>17.76</v>
+        <v>103.38</v>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: FRETE ECONÔMICO R$ 17,76 4 a 6 dias úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 103,38 7 dias úteis Correios PAC R$ 115,69 8 dias úteis Correios - PAC R$ 121,19 4 dias úteis Azul Cargo Express - e-commerce</t>
         </is>
       </c>
       <c r="P107" s="2" t="n"/>
@@ -7151,12 +7167,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – BANHEIRO INTERDITADO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -7165,42 +7181,46 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>57.935.095/0001-52</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/placas-de-avisos/placa-de-sinalizacao-bralimpia-banheiro-fora-de-uso-1-un/?PID=29836</t>
+          <t>https://www.ncbelladistribuidora.com.br/pa-coletora-preto-certec</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>Placa de Sinalização Bralimpia Banheiro Fora de Uso 1 UN</t>
+          <t>Pá Coletora Preto Certec</t>
         </is>
       </c>
       <c r="J108" s="6" t="n">
-        <v>74.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="K108" s="2" t="n"/>
-      <c r="L108" s="2" t="n"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo longo.</t>
+        </is>
+      </c>
       <c r="M108" s="6" t="n">
-        <v>74.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="N108" s="6" t="n">
-        <v>77.73</v>
+        <v>18.45</v>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Envio: Transportadora Valor: R$ 77,73</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,45 8 dias úteis Loggi - Express</t>
         </is>
       </c>
       <c r="P108" s="2" t="n"/>
@@ -7213,17 +7233,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
@@ -7231,38 +7251,36 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/placa-sinalisadora-piso-molhado</t>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-manuais/ferramentas-manuais/pa-para-lixo-c-cabo-100388</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Placa Sinalizadora Piso Molhado - Super Pro Bettanin</t>
+          <t>Pa Para Lixo C/ Cabo 100388</t>
         </is>
       </c>
       <c r="J109" s="6" t="n">
-        <v>59.59</v>
+        <v>20.9</v>
       </c>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="6" t="n">
-        <v>59.59</v>
-      </c>
-      <c r="N109" s="6" t="n">
-        <v>41.2</v>
-      </c>
+        <v>20.9</v>
+      </c>
+      <c r="N109" s="2" t="n"/>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 41,20 7 dias úteis Correios PAC</t>
+          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
         </is>
       </c>
       <c r="P109" s="2" t="n"/>
@@ -7275,56 +7293,56 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>General Clean</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>17.587.390/0001-40</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/placa-sinalizadora-piso-molhado-nobre</t>
+          <t>https://www.generalclean.com.br/pa-de-lixo-plastica-cabo-longo</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>Placa Sinalizadora Piso Molhado</t>
+          <t>PA DE LIXO PLASTICA CABO LONGO 40CM</t>
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>49.98</v>
+        <v>6.98</v>
       </c>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="6" t="n">
-        <v>49.98</v>
+        <v>6.98</v>
       </c>
       <c r="N110" s="6" t="n">
-        <v>32.18</v>
+        <v>46.6</v>
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 37,54 7 dias úteis Correios PAC R$ 43,28 8 dias úteis Correios - PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: CORREIOS PAC R$ 46,60 Previsto para 20/10/2026 até 22/10/2026</t>
         </is>
       </c>
       <c r="P110" s="2" t="n"/>
@@ -7337,12 +7355,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA DE LIXO – CABO LONGO - USO PROFISSIONAL.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -7351,46 +7369,42 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>50.970.342/0001-02</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/placas-de-avisos/placa-bettanin-sinalizadora-de-plastico-para-piso-molhado-1-un/?PID=74656</t>
+          <t>https://www.dutramaquinas.com.br/p/pa-coletora-de-lixo-cabo-de-madeira-revestido-com-plastico-pop-pp555</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>Placa Bettanin Sinalizadora de Plástico Para Piso Molhado 1 UN</t>
+          <t>Pá coletora de lixo cabo de madeira POP - PP555</t>
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>63.89</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
-        </is>
-      </c>
+      <c r="L111" s="2" t="n"/>
       <c r="M111" s="6" t="n">
-        <v>63.89</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>77.66</v>
+        <v>25.21</v>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,66 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: 8 a 10 dias úteis R$ 25,21</t>
         </is>
       </c>
       <c r="P111" s="2" t="n"/>
@@ -7403,12 +7417,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -7421,42 +7435,42 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>57.935.095/0001-52</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncbelladistribuidora.com.br/placa-sinal-piso-molhado-certec</t>
+          <t>https://www.gimba.com.br/pas-de-lixo/pa-coletora-com-cabo-bralimpia-pop-plastica-azul-pp555-1-un/?PID=25627</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>Placa Sinalizadora Piso Molhado Certec</t>
+          <t>Pá Coletora com Cabo Bralimpia Pop Plástica Azul PP555 1 UN</t>
         </is>
       </c>
       <c r="J112" s="6" t="n">
-        <v>39</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
+          <t>Característica não confirmada na página do produto: tampa basculante, cabo longo.</t>
         </is>
       </c>
       <c r="M112" s="6" t="n">
-        <v>39</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="N112" s="6" t="n">
-        <v>126.08</v>
+        <v>77.69</v>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 126,08 10 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,69 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P112" s="2" t="n"/>
@@ -7469,12 +7483,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
+          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -7483,46 +7497,46 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Melhoramentos Higiene</t>
+          <t>Casa do Saco de Lixo</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>01.517.623/0001-07</t>
+          <t>02.236.630/0001-95</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>https://melhoramentoshigiene.com.br/produto/placa-sinalizadora-piso-molhado-amarela/</t>
+          <t>https://loja.casadosacodelixo.com.br/pa-coletora-novica</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Placa sinalizadora piso molhado amarela – Bralimpia</t>
+          <t>Pá Coletora Noviça</t>
         </is>
       </c>
       <c r="J113" s="6" t="n">
-        <v>45.7</v>
+        <v>39.8</v>
       </c>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
+          <t>Característica não confirmada na página do produto: tampa basculante.</t>
         </is>
       </c>
       <c r="M113" s="6" t="n">
-        <v>45.7</v>
+        <v>39.8</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>29.02</v>
+        <v>27.42</v>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express (Entrega em 8 dias úteis) R$ 29,02</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P113" s="2" t="n"/>
@@ -7535,44 +7549,44 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
+          <t>PÁ COLETORA COM TAMPA BASCULANTE - CABO LONGO, USO INTERNO/EXTERNO.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Higienize</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>95.054.177/0001-87</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-de-plastico-bettanin-40cm-borracha-simples-com-cabo-1-un/?PID=74658</t>
+          <t>https://www.higienize.com/equipamentos/pa-coletora-com-tampa-bettanin</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>Rodo de Plástico Bettanin 40cm Borracha Simples com Cabo 1 UN</t>
+          <t>Pá Coletora com Tampa Bettanin</t>
         </is>
       </c>
       <c r="J114" s="6" t="n">
-        <v>29.9</v>
+        <v>58.49</v>
       </c>
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="inlineStr">
@@ -7581,14 +7595,14 @@
         </is>
       </c>
       <c r="M114" s="6" t="n">
-        <v>29.9</v>
+        <v>58.49</v>
       </c>
       <c r="N114" s="6" t="n">
-        <v>77.44</v>
+        <v>30.14</v>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,44 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 30,14 Previsto para 20/10/2026</t>
         </is>
       </c>
       <c r="P114" s="2" t="n"/>
@@ -7601,58 +7615,56 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
+          <t>PLACA SINALIZADORA – BANHEIRO INTERDITADO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>Profissional da Limpeza</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>45.343.703/0001-50</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/casa-e-lazer/limpeza/rodo-plastico-40cm-cabo-verde</t>
+          <t>https://profissionaldalimpeza.commercesuite.com.br/equipamentos/placa-de-sinalizacao/placa-de-sinalizacao-banheiro-fora-de-uso</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Rodo Plastico 40cm + Cabo Verde</t>
+          <t>Placa de Sinalização Banheiro Fora de Uso</t>
         </is>
       </c>
       <c r="J115" s="6" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="K115" s="2" t="n"/>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo longo.</t>
-        </is>
-      </c>
+      <c r="L115" s="2" t="n"/>
       <c r="M115" s="6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="N115" s="2" t="n"/>
+        <v>24.9</v>
+      </c>
+      <c r="N115" s="6" t="n">
+        <v>17.76</v>
+      </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
+          <t>Opção mais barata para o CEP 74933-130: FRETE ECONÔMICO R$ 17,76 4 a 6 dias úteis</t>
         </is>
       </c>
       <c r="P115" s="2" t="n"/>
@@ -7665,54 +7677,56 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
+          <t>PLACA SINALIZADORA – BANHEIRO INTERDITADO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>CASA DA LIMPEZA LTDA</t>
+          <t>Gimba</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>07.964.337/0001-68</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>https://casadalimpeza.net/produto/rodo-eco-40cm-c-cabo-14mts/</t>
+          <t>https://www.gimba.com.br/placas-de-avisos/placa-de-sinalizacao-bralimpia-banheiro-fora-de-uso-1-un/?PID=29836</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Rodo Eco 40cm c/cabo 1,4mts</t>
+          <t>Placa de Sinalização Bralimpia Banheiro Fora de Uso 1 UN</t>
         </is>
       </c>
       <c r="J116" s="6" t="n">
-        <v>38.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="6" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="N116" s="2" t="n"/>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="N116" s="6" t="n">
+        <v>77.73</v>
+      </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: Envio: Transportadora Valor: R$ 77,73</t>
         </is>
       </c>
       <c r="P116" s="2" t="n"/>
@@ -7725,17 +7739,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
+          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -7743,35 +7757,41 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="n"/>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/placa-sinalisadora-piso-molhado</t>
+        </is>
+      </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Rodo Prende Pano 40cm</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="n"/>
+          <t>Placa Sinalizadora Piso Molhado - Super Pro Bettanin</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>59.59</v>
+      </c>
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="n"/>
-      <c r="M117" s="2" t="n"/>
-      <c r="N117" s="2" t="n"/>
+      <c r="M117" s="6" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="N117" s="6" t="n">
+        <v>41.2</v>
+      </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P117" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/produto/rodo-prende-pano-40cm.html</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: R$ 41,20 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7781,17 +7801,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>RODO – 60 CM - BASE COM BORRACHA DUPLA; CABO LONGO.</t>
+          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -7799,38 +7819,38 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-de-plastico-brubalar-duplo-para-chao-60cm-com-cabo-de-madeira-revestido-120m-1-un/?PID=78781</t>
+          <t>https://www.supriflex.com.br/placa-sinalizadora-piso-molhado-nobre</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>Rodo de Plástico Brubalar Duplo para Chão 60cm com Cabo de Madeira Revestido 1,20m 1 UN</t>
+          <t>Placa Sinalizadora Piso Molhado</t>
         </is>
       </c>
       <c r="J118" s="6" t="n">
-        <v>18.59</v>
+        <v>49.98</v>
       </c>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="6" t="n">
-        <v>18.59</v>
+        <v>49.98</v>
       </c>
       <c r="N118" s="6" t="n">
-        <v>77.36</v>
+        <v>32.18</v>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,36 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 37,54 7 dias úteis Correios PAC R$ 43,28 8 dias úteis Correios - PAC</t>
         </is>
       </c>
       <c r="P118" s="2" t="n"/>
@@ -7843,17 +7863,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS - COM CABO.</t>
+          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -7861,38 +7881,42 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/rodo-multiuso-para-pia-e-vidros-255-cm-com-cabo-emborrachado-powermaid</t>
+          <t>https://www.gimba.com.br/placas-de-avisos/placa-bettanin-sinalizadora-de-plastico-para-piso-molhado-1-un/?PID=74656</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Rodo Multiuso para Pia e Vidros 25,5 cm com Cabo Emborrachado – Powermaid</t>
+          <t>Placa Bettanin Sinalizadora de Plástico Para Piso Molhado 1 UN</t>
         </is>
       </c>
       <c r="J119" s="6" t="n">
-        <v>7.9</v>
+        <v>63.89</v>
       </c>
       <c r="K119" s="2" t="n"/>
-      <c r="L119" s="2" t="n"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
+        </is>
+      </c>
       <c r="M119" s="6" t="n">
-        <v>7.9</v>
+        <v>63.89</v>
       </c>
       <c r="N119" s="6" t="n">
-        <v>36.64</v>
+        <v>77.66</v>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,66 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P119" s="2" t="n"/>
@@ -7905,12 +7929,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS - COM CABO.</t>
+          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7933,32 +7957,32 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncbelladistribuidora.com.br/rodo-limpa-vidros-com-dispenser-25cm-superpro-bettanin</t>
+          <t>https://www.ncbelladistribuidora.com.br/placa-sinal-piso-molhado-certec</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>Rodo Limpa Vidros Com Dispenser 25Cm SuperPro Bettanin</t>
+          <t>Placa Sinalizadora Piso Molhado Certec</t>
         </is>
       </c>
       <c r="J120" s="6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K120" s="2" t="n"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: com cabo.</t>
+          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
         </is>
       </c>
       <c r="M120" s="6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N120" s="6" t="n">
-        <v>49.83</v>
+        <v>126.08</v>
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 49,83 7 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 126,08 10 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P120" s="2" t="n"/>
@@ -7971,12 +7995,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS - COM CABO.</t>
+          <t>PLACA SINALIZADORA – PISO MOLHADO/ESCORREGADIO - DOBRÁVEL/PORTÁTIL.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7985,7 +8009,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -7999,28 +8023,32 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>https://melhoramentoshigiene.com.br/produto/rodo-limpa-vidros-25cm-combinado-2-em-1-com-cabo/</t>
+          <t>https://melhoramentoshigiene.com.br/produto/placa-sinalizadora-piso-molhado-amarela/</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Rodo limpa vidros 25cm – Combinado 2 Em 1 – Com Cabo – Bralimpia</t>
+          <t>Placa sinalizadora piso molhado amarela – Bralimpia</t>
         </is>
       </c>
       <c r="J121" s="6" t="n">
-        <v>80</v>
+        <v>45.7</v>
       </c>
       <c r="K121" s="2" t="n"/>
-      <c r="L121" s="2" t="n"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: dobrável/portátil.</t>
+        </is>
+      </c>
       <c r="M121" s="6" t="n">
-        <v>80</v>
+        <v>45.7</v>
       </c>
       <c r="N121" s="6" t="n">
-        <v>28.6</v>
+        <v>29.02</v>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Entrega em 9 dias úteis) R$ 28,60</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express (Entrega em 8 dias úteis) R$ 29,02</t>
         </is>
       </c>
       <c r="P121" s="2" t="n"/>
@@ -8033,12 +8061,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS - COM CABO.</t>
+          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -8051,7 +8079,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -8061,28 +8089,32 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-limpa-vidros-nobre-com-cabo-plastico-1-un/?PID=71996</t>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-de-plastico-bettanin-40cm-borracha-simples-com-cabo-1-un/?PID=74658</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>Rodo Limpa Vidros Nobre com Cabo Plástico 1 UN</t>
+          <t>Rodo de Plástico Bettanin 40cm Borracha Simples com Cabo 1 UN</t>
         </is>
       </c>
       <c r="J122" s="6" t="n">
-        <v>66.48999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="K122" s="2" t="n"/>
-      <c r="L122" s="2" t="n"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo longo.</t>
+        </is>
+      </c>
       <c r="M122" s="6" t="n">
-        <v>66.48999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="N122" s="6" t="n">
-        <v>77.67</v>
+        <v>77.44</v>
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,67 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,44 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P122" s="2" t="n"/>
@@ -8095,60 +8127,58 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS - COM CABO.</t>
+          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Higienize</t>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>95.054.177/0001-87</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>https://www.higienize.com/equipamentos/rodo-limpa-vidros-combinado-35-cm-bralimpia</t>
+          <t>https://www.fermarcsferramentas.com.br/casa-e-lazer/limpeza/rodo-plastico-40cm-cabo-verde</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Rodo Limpa Vidros Combinado 35 cm Bralimpia</t>
+          <t>Rodo Plastico 40cm + Cabo Verde</t>
         </is>
       </c>
       <c r="J123" s="6" t="n">
-        <v>118.55</v>
+        <v>22.5</v>
       </c>
       <c r="K123" s="2" t="n"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: com cabo.</t>
+          <t>Característica não confirmada na página do produto: cabo longo.</t>
         </is>
       </c>
       <c r="M123" s="6" t="n">
-        <v>118.55</v>
-      </c>
-      <c r="N123" s="6" t="n">
-        <v>29.46</v>
-      </c>
+        <v>22.5</v>
+      </c>
+      <c r="N123" s="2" t="n"/>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 29,46 Previsto para 20/10/2026</t>
+          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
         </is>
       </c>
       <c r="P123" s="2" t="n"/>
@@ -8161,17 +8191,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
+          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -8179,42 +8209,36 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>CASA DA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>07.964.337/0001-68</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/produto/rodo-limpa-vidro-35cm-moppita.html</t>
+          <t>https://casadalimpeza.net/produto/rodo-eco-40cm-c-cabo-14mts/</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Rodo limpa vidro 35cm - moppita</t>
+          <t>Rodo Eco 40cm c/cabo 1,4mts</t>
         </is>
       </c>
       <c r="J124" s="6" t="n">
-        <v>48.74</v>
+        <v>38.4</v>
       </c>
       <c r="K124" s="2" t="n"/>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo extensível.</t>
-        </is>
-      </c>
+      <c r="L124" s="2" t="n"/>
       <c r="M124" s="6" t="n">
-        <v>48.74</v>
-      </c>
-      <c r="N124" s="6" t="n">
-        <v>36.91</v>
-      </c>
+        <v>38.4</v>
+      </c>
+      <c r="N124" s="2" t="n"/>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 36,91 7 dias úteis Correios PAC</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P124" s="2" t="n"/>
@@ -8227,12 +8251,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
+          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -8240,47 +8264,49 @@
           <t>RS</t>
         </is>
       </c>
-      <c r="E125" s="4" t="n">
-        <v>46308</v>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>91.845.735/0004-14</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/rodo-combinado-limpa-vidros-35cm-ref-d098</t>
+          <t>https://www.lfmaquinaseferramentas.com.br/1125--rodo-eva-40cm-12x1-57958/p</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>Rodo Combinado Limpa Vidros 35cm Ref.: D098</t>
+          <t>1125 RODO EVA 40CM 12X1</t>
         </is>
       </c>
       <c r="J125" s="6" t="n">
-        <v>79.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="K125" s="2" t="n"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: cabo extensível.</t>
+          <t>Base de EVA aceita como borracha (decisão de 14/10/2026); comprimento do cabo não confirmado na página.</t>
         </is>
       </c>
       <c r="M125" s="6" t="n">
-        <v>79.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="N125" s="6" t="n">
-        <v>32.18</v>
+        <v>14.92</v>
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 35,04 7 dias úteis Correios PAC R$ 40,71 8 dias úteis Correios - PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: Em até 7 dias úteis R$ 14,92</t>
         </is>
       </c>
       <c r="P125" s="2" t="n"/>
@@ -8293,17 +8319,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
+          <t>RODO – 40 CM - BASE COM BORRACHA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -8311,45 +8337,35 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-para-limpeza-de-vidros-bralimpia-2-em-1-25cm-com-cabo-cb250-1-un/?PID=38493</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n"/>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Rodo para Limpeza de Vidros Bralimpia 2 em 1 25cm com Cabo CB250 1 UN</t>
-        </is>
-      </c>
-      <c r="J126" s="6" t="n">
-        <v>83.69</v>
-      </c>
+          <t>Rodo Prende Pano 40cm</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="n"/>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cabo extensível.</t>
-        </is>
-      </c>
-      <c r="M126" s="6" t="n">
-        <v>83.69</v>
-      </c>
-      <c r="N126" s="6" t="n">
-        <v>77.79000000000001</v>
-      </c>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,79 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
-        </is>
-      </c>
-      <c r="P126" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/rodo-prende-pano-40cm.html</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8359,12 +8375,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
+          <t>RODO – 60 CM - BASE COM BORRACHA DUPLA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -8372,47 +8388,49 @@
           <t>RS</t>
         </is>
       </c>
-      <c r="E127" s="4" t="n">
-        <v>46308</v>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>91.845.735/0004-14</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/rodo-de-pia</t>
+          <t>https://www.lfmaquinaseferramentas.com.br/1128-rodo-60cm-12x1-57947/p</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>Rodo de Pia</t>
+          <t>1128 RODO 60CM 12X1</t>
         </is>
       </c>
       <c r="J127" s="6" t="n">
-        <v>14.23</v>
+        <v>48.9</v>
       </c>
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: plástico, medida 13 cm.</t>
+          <t>Característica não confirmada na página do produto: borracha dupla, cabo longo.</t>
         </is>
       </c>
       <c r="M127" s="6" t="n">
-        <v>14.23</v>
+        <v>48.9</v>
       </c>
       <c r="N127" s="6" t="n">
-        <v>31.54</v>
+        <v>14.92</v>
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 36,14 8 dias úteis Correios - PAC R$ 41,80 6 dias úteis Jadlog - .Com</t>
+          <t>Opção mais barata para o CEP 74933-130: Em até 7 dias úteis R$ 14,92</t>
         </is>
       </c>
       <c r="P127" s="2" t="n"/>
@@ -8425,12 +8443,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
+          <t>RODO – 60 CM - BASE COM BORRACHA DUPLA; CABO LONGO.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -8443,7 +8461,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Gimba</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8453,32 +8471,28 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/acessorios-para-pia/rodo-de-pia-dsr-de-plastico-1-un/?PID=79082</t>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-de-plastico-brubalar-duplo-para-chao-60cm-com-cabo-de-madeira-revestido-120m-1-un/?PID=78781</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Rodo de Pia DSR de Plástico 1 UN</t>
+          <t>Rodo de Plástico Brubalar Duplo para Chão 60cm com Cabo de Madeira Revestido 1,20m 1 UN</t>
         </is>
       </c>
       <c r="J128" s="6" t="n">
-        <v>1.99</v>
+        <v>18.59</v>
       </c>
       <c r="K128" s="2" t="n"/>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: medida 13 cm.</t>
-        </is>
-      </c>
+      <c r="L128" s="2" t="n"/>
       <c r="M128" s="6" t="n">
-        <v>1.99</v>
+        <v>18.59</v>
       </c>
       <c r="N128" s="6" t="n">
-        <v>30.13</v>
+        <v>77.36</v>
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,13 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,36 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P128" s="2" t="n"/>
@@ -8491,56 +8505,56 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
+          <t>RODO PARA VIDROS - COM CABO.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>PreveOeste</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>01.974.824/0001-25</t>
+          <t>58.509.800/0001-12</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>https://www.preveoeste.com.br/rodo-pia-pequeno-1633-p107106</t>
+          <t>https://www.starsprodutosdelimpeza.com.br/rodo-multiuso-para-pia-e-vidros-255-cm-com-cabo-emborrachado-powermaid</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>RODO PIA PEQUENO</t>
+          <t>Rodo Multiuso para Pia e Vidros 25,5 cm com Cabo Emborrachado – Powermaid</t>
         </is>
       </c>
       <c r="J129" s="6" t="n">
-        <v>13.9</v>
+        <v>7.9</v>
       </c>
       <c r="K129" s="2" t="n"/>
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="6" t="n">
-        <v>13.9</v>
+        <v>7.9</v>
       </c>
       <c r="N129" s="6" t="n">
-        <v>24.45</v>
+        <v>36.64</v>
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 24,45 5 dia(s) útil(eis)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P129" s="2" t="n"/>
@@ -8553,60 +8567,60 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
+          <t>RODO PARA VIDROS - COM CABO.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Casa do Saco de Lixo</t>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>02.236.630/0001-95</t>
+          <t>57.935.095/0001-52</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>https://loja.casadosacodelixo.com.br/vassoura-de-piacava-perovinha</t>
+          <t>https://www.ncbelladistribuidora.com.br/rodo-limpa-vidros-com-dispenser-25cm-superpro-bettanin</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>Vassoura de piaçava - Perovinha</t>
+          <t>Rodo Limpa Vidros Com Dispenser 25Cm SuperPro Bettanin</t>
         </is>
       </c>
       <c r="J130" s="6" t="n">
-        <v>15.5</v>
+        <v>45</v>
       </c>
       <c r="K130" s="2" t="n"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: cerdas duras.</t>
+          <t>Característica não confirmada na página do produto: com cabo.</t>
         </is>
       </c>
       <c r="M130" s="6" t="n">
-        <v>15.5</v>
+        <v>45</v>
       </c>
       <c r="N130" s="6" t="n">
-        <v>37.46</v>
+        <v>49.83</v>
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 37,46 5 dias úteis Jadlog - .Com</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 49,83 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P130" s="2" t="n"/>
@@ -8619,17 +8633,17 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
+          <t>RODO PARA VIDROS - COM CABO.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -8637,42 +8651,38 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>LF Máquinas e Ferramentas</t>
+          <t>Melhoramentos Higiene</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>91.845.735/0004-14</t>
+          <t>01.517.623/0001-07</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>https://www.lfmaquinaseferramentas.com.br/vassoura-piacava-luvano-beta-comercial/p?skuId=27442</t>
+          <t>https://melhoramentoshigiene.com.br/produto/rodo-limpa-vidros-25cm-combinado-2-em-1-com-cabo/</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>Vassoura De Piaçava Luvano Modelo Beta Comercial</t>
+          <t>Rodo limpa vidros 25cm – Combinado 2 Em 1 – Com Cabo – Bralimpia</t>
         </is>
       </c>
       <c r="J131" s="6" t="n">
-        <v>47.78</v>
+        <v>80</v>
       </c>
       <c r="K131" s="2" t="n"/>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cerdas duras.</t>
-        </is>
-      </c>
+      <c r="L131" s="2" t="n"/>
       <c r="M131" s="6" t="n">
-        <v>47.78</v>
+        <v>80</v>
       </c>
       <c r="N131" s="6" t="n">
-        <v>19.67</v>
+        <v>28.6</v>
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Padrão 6bd</t>
+          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Entrega em 9 dias úteis) R$ 28,60</t>
         </is>
       </c>
       <c r="P131" s="2" t="n"/>
@@ -8685,12 +8695,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
+          <t>RODO PARA VIDROS - COM CABO.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -8699,46 +8709,42 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Dutra Máquinas</t>
+          <t>Gimba</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>50.970.342/0001-02</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>https://www.dutramaquinas.com.br/p/vassoura-tipo-gari-de-piacava-cepa-plastica-60-cm-60018</t>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-limpa-vidros-nobre-com-cabo-plastico-1-un/?PID=71996</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Vassoura tipo gari de piaçava cepa plastica 60 cm</t>
+          <t>Rodo Limpa Vidros Nobre com Cabo Plástico 1 UN</t>
         </is>
       </c>
       <c r="J132" s="6" t="n">
-        <v>93.90000000000001</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K132" s="2" t="n"/>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cerdas duras.</t>
-        </is>
-      </c>
+      <c r="L132" s="2" t="n"/>
       <c r="M132" s="6" t="n">
-        <v>93.90000000000001</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="N132" s="6" t="n">
-        <v>56.54</v>
+        <v>77.67</v>
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 56,54</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,67 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P132" s="2" t="n"/>
@@ -8751,56 +8757,60 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+          <t>RODO PARA VIDROS - COM CABO.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>Higienize</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>95.054.177/0001-87</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/produto/vassoura-de-palha-caipira-especial-c-cabo-dsr.html</t>
+          <t>https://www.higienize.com/equipamentos/rodo-limpa-vidros-combinado-35-cm-bralimpia</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Vassoura de Palha Caipira Especial c/cabo - DSR</t>
+          <t>Rodo Limpa Vidros Combinado 35 cm Bralimpia</t>
         </is>
       </c>
       <c r="J133" s="6" t="n">
-        <v>58.7</v>
+        <v>118.55</v>
       </c>
       <c r="K133" s="2" t="n"/>
-      <c r="L133" s="2" t="n"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: com cabo.</t>
+        </is>
+      </c>
       <c r="M133" s="6" t="n">
-        <v>58.7</v>
+        <v>118.55</v>
       </c>
       <c r="N133" s="6" t="n">
-        <v>37.04</v>
+        <v>29.46</v>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 37,04 7 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 29,46 Previsto para 20/10/2026</t>
         </is>
       </c>
       <c r="P133" s="2" t="n"/>
@@ -8813,17 +8823,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -8831,38 +8841,42 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>58.509.800/0001-12</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/produto/vassoura-de-palha-d154.html</t>
+          <t>https://www.starsprodutosdelimpeza.com.br/produto/rodo-limpa-vidro-35cm-moppita.html</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Vassoura de Palha D154</t>
+          <t>Rodo limpa vidro 35cm - moppita</t>
         </is>
       </c>
       <c r="J134" s="6" t="n">
-        <v>29.8</v>
+        <v>48.74</v>
       </c>
       <c r="K134" s="2" t="n"/>
-      <c r="L134" s="2" t="n"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo extensível.</t>
+        </is>
+      </c>
       <c r="M134" s="6" t="n">
-        <v>29.8</v>
+        <v>48.74</v>
       </c>
       <c r="N134" s="6" t="n">
-        <v>41.8</v>
+        <v>36.91</v>
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 41,80 6 dias úteis Jadlog - .Com R$ 73,82 7 dias úteis Jadlog - .Package</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,91 7 dias úteis Correios PAC</t>
         </is>
       </c>
       <c r="P134" s="2" t="n"/>
@@ -8875,17 +8889,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -8893,38 +8907,42 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-de-palha-caicara-5-fios-com-cabo-1-un/?PID=101576</t>
+          <t>https://www.supriflex.com.br/rodo-combinado-limpa-vidros-35cm-ref-d098</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>Vassoura de Palha Caiçara 5 Fios com Cabo 1 UN</t>
+          <t>Rodo Combinado Limpa Vidros 35cm Ref.: D098</t>
         </is>
       </c>
       <c r="J135" s="6" t="n">
-        <v>42.99</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K135" s="2" t="n"/>
-      <c r="L135" s="2" t="n"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo extensível.</t>
+        </is>
+      </c>
       <c r="M135" s="6" t="n">
-        <v>42.99</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="N135" s="6" t="n">
-        <v>77.52</v>
+        <v>32.18</v>
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,52 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 32,18 7 dias úteis Jadlog - .Package R$ 35,04 7 dias úteis Correios PAC R$ 40,71 8 dias úteis Correios - PAC</t>
         </is>
       </c>
       <c r="P135" s="2" t="n"/>
@@ -8937,12 +8955,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+          <t>RODO PARA VIDROS COM CABO EXTENSÍVEL - PARA LIMPEZA DE VIDROS EM ALTURA.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -8951,42 +8969,46 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>General Clean</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>17.587.390/0001-40</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>https://www.generalclean.com.br/vassoura-de-palha</t>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/rodo-para-limpeza-de-vidros-bralimpia-2-em-1-25cm-com-cabo-cb250-1-un/?PID=38493</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PALHA</t>
+          <t>Rodo para Limpeza de Vidros Bralimpia 2 em 1 25cm com Cabo CB250 1 UN</t>
         </is>
       </c>
       <c r="J136" s="6" t="n">
-        <v>39.82</v>
+        <v>83.69</v>
       </c>
       <c r="K136" s="2" t="n"/>
-      <c r="L136" s="2" t="n"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cabo extensível.</t>
+        </is>
+      </c>
       <c r="M136" s="6" t="n">
-        <v>39.82</v>
+        <v>83.69</v>
       </c>
       <c r="N136" s="6" t="n">
-        <v>31.62</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .COM R$ 31,62 Previsto para 15/10/2026 até 19/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,79 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P136" s="2" t="n"/>
@@ -8999,56 +9021,60 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Casa do Saco de Lixo</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>02.236.630/0001-95</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>https://loja.casadosacodelixo.com.br/vassoura-de-palha-4-fios-perovinha</t>
+          <t>https://www.supriflex.com.br/rodo-de-pia</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Vassoura de Palha 4 fios - Perovinha</t>
+          <t>Rodo de Pia</t>
         </is>
       </c>
       <c r="J137" s="6" t="n">
-        <v>39.9</v>
+        <v>14.23</v>
       </c>
       <c r="K137" s="2" t="n"/>
-      <c r="L137" s="2" t="n"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: plástico, medida 13 cm.</t>
+        </is>
+      </c>
       <c r="M137" s="6" t="n">
-        <v>39.9</v>
+        <v>14.23</v>
       </c>
       <c r="N137" s="6" t="n">
-        <v>67.45</v>
+        <v>31.54</v>
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 67,45 6 dias úteis Jadlog - .Package</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 36,14 8 dias úteis Correios - PAC R$ 41,80 6 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P137" s="2" t="n"/>
@@ -9061,17 +9087,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 30 CM - PARA LIMPEZA GERAL.</t>
+          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -9079,38 +9105,42 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>54.651.716/0011-50</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-30cm-plastica-sintetica-scabo-dsr</t>
+          <t>https://www.gimba.com.br/acessorios-para-pia/rodo-de-pia-dsr-de-plastico-1-un/?PID=79082</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Vassoura pelo 30cm Plástica Sintética S/Cabo - DSR</t>
+          <t>Rodo de Pia DSR de Plástico 1 UN</t>
         </is>
       </c>
       <c r="J138" s="6" t="n">
-        <v>10.5</v>
+        <v>1.99</v>
       </c>
       <c r="K138" s="2" t="n"/>
-      <c r="L138" s="2" t="n"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: medida 13 cm.</t>
+        </is>
+      </c>
       <c r="M138" s="6" t="n">
-        <v>10.5</v>
+        <v>1.99</v>
       </c>
       <c r="N138" s="6" t="n">
-        <v>36.64</v>
+        <v>30.13</v>
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,13 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
       <c r="P138" s="2" t="n"/>
@@ -9123,56 +9153,62 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 30 CM - PARA LIMPEZA GERAL.</t>
+          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>46308</v>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>PLAST HOUSE LTDA (Plast House)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>52.081.713/0001-20</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-pelo-sintetico-brubalar-30cm-cabo-s10-alegria-1-un/?PID=78790</t>
+          <t>https://plasthouse.com.br/produto/casa/cozinha/outrios-itens-de-cozinha/rodo-de-pia-sanremo/</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>Vassoura Pêlo Sintético Brubalar 30cm Cabo S10 Alegria 1 UN</t>
+          <t>Rodo de Pia - Sanremo</t>
         </is>
       </c>
       <c r="J139" s="6" t="n">
-        <v>15.99</v>
+        <v>5.3</v>
       </c>
       <c r="K139" s="2" t="n"/>
-      <c r="L139" s="2" t="n"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: aproximadamente 13 cm.</t>
+        </is>
+      </c>
       <c r="M139" s="6" t="n">
-        <v>15.99</v>
+        <v>5.3</v>
       </c>
       <c r="N139" s="6" t="n">
-        <v>77.34999999999999</v>
+        <v>28.85</v>
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,35 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: JeT Standard (Melhor Envio) (11 a 13 dias úteis): R$ 28,85</t>
         </is>
       </c>
       <c r="P139" s="2" t="n"/>
@@ -9185,56 +9221,56 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 40 CM - PARA LIMPEZA GERAL.</t>
+          <t>RODO PARA PIA - PLÁSTICO; APROXIMADAMENTE 13 CM.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+          <t>PreveOeste</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>58.509.800/0001-12</t>
+          <t>01.974.824/0001-25</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-40cm-plastica-sintetica-scabo-dsr</t>
+          <t>https://www.preveoeste.com.br/rodo-pia-pequeno-1633-p107106</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Vassoura pelo 40cm Plástica Sintética S/Cabo - DSR</t>
+          <t>RODO PIA PEQUENO</t>
         </is>
       </c>
       <c r="J140" s="6" t="n">
-        <v>22.9</v>
+        <v>13.9</v>
       </c>
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="6" t="n">
-        <v>22.9</v>
+        <v>13.9</v>
       </c>
       <c r="N140" s="6" t="n">
-        <v>36.64</v>
+        <v>24.45</v>
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 24,45 5 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P140" s="2" t="n"/>
@@ -9247,56 +9283,60 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 40 CM - PARA LIMPEZA GERAL.</t>
+          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>Casa do Saco de Lixo</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>02.236.630/0001-95</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-brubalar-de-pelo-sintetico-com-cabo-120m-40cm-1-un/?PID=78791</t>
+          <t>https://loja.casadosacodelixo.com.br/vassoura-de-piacava-perovinha</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Vassoura Brubalar de Pelo Sintético com Cabo 1,20m 40cm 1 UN</t>
+          <t>Vassoura de piaçava - Perovinha</t>
         </is>
       </c>
       <c r="J141" s="6" t="n">
-        <v>18.69</v>
+        <v>15.5</v>
       </c>
       <c r="K141" s="2" t="n"/>
-      <c r="L141" s="2" t="n"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cerdas duras.</t>
+        </is>
+      </c>
       <c r="M141" s="6" t="n">
-        <v>18.69</v>
+        <v>15.5</v>
       </c>
       <c r="N141" s="6" t="n">
-        <v>77.36</v>
+        <v>37.46</v>
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,36 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 37,46 5 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P141" s="2" t="n"/>
@@ -9309,56 +9349,62 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>46308</v>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>01.974.824/0001-25</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-brubalar-pelo-sintetico-60cm-cabo-120m-carmela-1-un/?PID=78789</t>
+          <t>https://www.preveoeste.com.br/vassoura-super-tupy-cerdas-longas-com-cabo-120mt-2075-p140926</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Vassoura Brubalar Pelo Sintético 60cm Cabo 1,20m Carmela 1 UN</t>
+          <t>Vassoura Super Tupy Cerdas Longas Com Cabo 1,20mt</t>
         </is>
       </c>
       <c r="J142" s="6" t="n">
-        <v>23.29</v>
+        <v>33.9</v>
       </c>
       <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cerdas duras.</t>
+        </is>
+      </c>
       <c r="M142" s="6" t="n">
-        <v>23.29</v>
+        <v>33.9</v>
       </c>
       <c r="N142" s="6" t="n">
-        <v>77.40000000000001</v>
+        <v>22.76</v>
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,40 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 22,76 5 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P142" s="2" t="n"/>
@@ -9371,58 +9417,60 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+          <t>LF Máquinas e Ferramentas</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>91.845.735/0004-14</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/jardinagem-e-agricultura/combustao/vassoura-pelo-60cm-cabo-preto-60115</t>
+          <t>https://www.lfmaquinaseferramentas.com.br/vassoura-piacava-luvano-beta-comercial/p?skuId=27442</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>Vassoura Pelo 60cm+Cabo Preto 60115</t>
+          <t>Vassoura De Piaçava Luvano Modelo Beta Comercial</t>
         </is>
       </c>
       <c r="J143" s="6" t="n">
-        <v>76.5</v>
+        <v>47.78</v>
       </c>
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: pelo sintético.</t>
+          <t>Característica não confirmada na página do produto: cerdas duras.</t>
         </is>
       </c>
       <c r="M143" s="6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="N143" s="2" t="n"/>
+        <v>47.78</v>
+      </c>
+      <c r="N143" s="6" t="n">
+        <v>19.67</v>
+      </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Padrão 6bd</t>
         </is>
       </c>
       <c r="P143" s="2" t="n"/>
@@ -9435,12 +9483,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -9449,46 +9497,46 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>General Clean</t>
+          <t>Dutra Máquinas</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>17.587.390/0001-40</t>
+          <t>50.970.342/0001-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>https://www.generalclean.com.br/vassoura-pelo-60cm-sem-cabo</t>
+          <t>https://www.dutramaquinas.com.br/p/vassoura-tipo-gari-de-piacava-cepa-plastica-60-cm-60018</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA PELO 60CM SEM CABO</t>
+          <t>Vassoura tipo gari de piaçava cepa plastica 60 cm</t>
         </is>
       </c>
       <c r="J144" s="6" t="n">
-        <v>20.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: pelo sintético.</t>
+          <t>Característica não confirmada na página do produto: cerdas duras.</t>
         </is>
       </c>
       <c r="M144" s="6" t="n">
-        <v>20.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N144" s="6" t="n">
-        <v>21.36</v>
+        <v>56.54</v>
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .PACKAGE R$ 21,36 Previsto para 16/10/2026 até 20/10/2026</t>
+          <t>Opção mais barata para o CEP 74933-130: 3 a 6 dias úteis R$ 56,54</t>
         </is>
       </c>
       <c r="P144" s="2" t="n"/>
@@ -9501,12 +9549,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -9527,27 +9575,33 @@
           <t>58.509.800/0001-12</t>
         </is>
       </c>
-      <c r="H145" s="2" t="n"/>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/produto/vassoura-de-palha-caipira-especial-c-cabo-dsr.html</t>
+        </is>
+      </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>Vassoura pelo 60cm Plástica Sintética 50 S/Cabo - DSR</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n"/>
+          <t>Vassoura de Palha Caipira Especial c/cabo - DSR</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>58.7</v>
+      </c>
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="n"/>
-      <c r="M145" s="2" t="n"/>
-      <c r="N145" s="2" t="n"/>
+      <c r="M145" s="6" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="N145" s="6" t="n">
+        <v>37.04</v>
+      </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P145" s="5" t="inlineStr">
-        <is>
-          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-60cm-plastica-sintetica-scabo-dsr</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: R$ 37,04 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9557,17 +9611,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>VASSOURA DE TETO/VASCULHO - CERDAS DE NYLON; CABO LONGO.</t>
+          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -9575,44 +9629,788 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-limpa-teto-mm-vassouras-nylon-cb-2-metros-1-un/?PID=207242</t>
+          <t>https://www.supriflex.com.br/produto/vassoura-de-palha-d154.html</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Vassoura Limpa Teto MM Vassouras Nylon CB 2 Metros 1 UN</t>
+          <t>Vassoura de Palha D154</t>
         </is>
       </c>
       <c r="J146" s="6" t="n">
-        <v>34.9</v>
+        <v>29.8</v>
       </c>
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="N146" s="6" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 41,80 6 dias úteis Jadlog - .Com R$ 73,82 7 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-de-palha-caicara-5-fios-com-cabo-1-un/?PID=101576</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura de Palha Caiçara 5 Fios com Cabo 1 UN</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="K147" s="2" t="n"/>
+      <c r="L147" s="2" t="n"/>
+      <c r="M147" s="6" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="N147" s="6" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,52 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>General Clean</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>17.587.390/0001-40</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>https://www.generalclean.com.br/vassoura-de-palha</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PALHA</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="K148" s="2" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="6" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="N148" s="6" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .COM R$ 31,62 Previsto para 15/10/2026 até 19/10/2026</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE CERDAS NATURAIS/PALHA - PARA ÁREAS EXTERNAS.</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Casa do Saco de Lixo</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/vassoura-de-palha-4-fios-perovinha</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura de Palha 4 fios - Perovinha</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K149" s="2" t="n"/>
+      <c r="L149" s="2" t="n"/>
+      <c r="M149" s="6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="N149" s="6" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 67,45 6 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 30 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-30cm-plastica-sintetica-scabo-dsr</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura pelo 30cm Plástica Sintética S/Cabo - DSR</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K150" s="2" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N150" s="6" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 30 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-pelo-sintetico-brubalar-30cm-cabo-s10-alegria-1-un/?PID=78790</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Pêlo Sintético Brubalar 30cm Cabo S10 Alegria 1 UN</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="K151" s="2" t="n"/>
+      <c r="L151" s="2" t="n"/>
+      <c r="M151" s="6" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="N151" s="6" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,35 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 40 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-40cm-plastica-sintetica-scabo-dsr</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura pelo 40cm Plástica Sintética S/Cabo - DSR</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="N152" s="6" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 40 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-brubalar-de-pelo-sintetico-com-cabo-120m-40cm-1-un/?PID=78791</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Brubalar de Pelo Sintético com Cabo 1,20m 40cm 1 UN</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="K153" s="2" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="6" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="N153" s="6" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,36 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-brubalar-pelo-sintetico-60cm-cabo-120m-carmela-1-un/?PID=78789</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Brubalar Pelo Sintético 60cm Cabo 1,20m Carmela 1 UN</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K154" s="2" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="6" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="N154" s="6" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,40 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/jardinagem-e-agricultura/combustao/vassoura-pelo-60cm-cabo-preto-60115</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Pelo 60cm+Cabo Preto 60115</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K155" s="2" t="n"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: pelo sintético.</t>
+        </is>
+      </c>
+      <c r="M155" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>Frete não calculado (GO para GO) | frete real: R$ 51,59</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>General Clean</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>17.587.390/0001-40</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>https://www.generalclean.com.br/vassoura-pelo-60cm-sem-cabo</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA PELO 60CM SEM CABO</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K156" s="2" t="n"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: pelo sintético.</t>
+        </is>
+      </c>
+      <c r="M156" s="6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N156" s="6" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="O156" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .PACKAGE R$ 21,36 Previsto para 16/10/2026 até 20/10/2026</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n"/>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura pelo 60cm Plástica Sintética 50 S/Cabo - DSR</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="n"/>
+      <c r="L157" s="2" t="n"/>
+      <c r="M157" s="2" t="n"/>
+      <c r="N157" s="2" t="n"/>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-60cm-plastica-sintetica-scabo-dsr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE TETO/VASCULHO - CERDAS DE NYLON; CABO LONGO.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Gimba</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/vassouras-e-rodos/vassoura-limpa-teto-mm-vassouras-nylon-cb-2-metros-1-un/?PID=207242</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Limpa Teto MM Vassouras Nylon CB 2 Metros 1 UN</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="n">
         <v>34.9</v>
       </c>
-      <c r="N146" s="6" t="n">
+      <c r="K158" s="2" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="6" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="N158" s="6" t="n">
         <v>77.47</v>
       </c>
-      <c r="O146" s="3" t="inlineStr">
+      <c r="O158" s="3" t="inlineStr">
         <is>
           <t>Opção mais barata para o CEP 74933-130: Valor: R$ 77,47 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
         </is>
       </c>
-      <c r="P146" s="2" t="n"/>
+      <c r="P158" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P146"/>
+  <autoFilter ref="A1:P158"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -9678,43 +10476,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
@@ -9729,7 +10527,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
@@ -9738,7 +10536,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId128"/>
@@ -9757,8 +10555,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
